--- a/reports/Debug-purgatory-20260111/For The Week Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260111/For The Week Ending (Actual)_Revenue.xlsx
@@ -103,7 +103,7 @@
     <t>D4053</t>
   </si>
   <si>
-    <t xml:space="preserve">D4054                    </t>
+    <t>D4054</t>
   </si>
   <si>
     <t>D4055</t>
